--- a/chapters/08/python_analytics/AIHE-PY15_probabilistic_sensitivity_analysis_ceac_and_evpi/data/xlsx/15_probabilistic_sensitivity_ceac_evpi_sample.xlsx
+++ b/chapters/08/python_analytics/AIHE-PY15_probabilistic_sensitivity_analysis_ceac_and_evpi/data/xlsx/15_probabilistic_sensitivity_ceac_evpi_sample.xlsx
@@ -81,7 +81,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,7 +89,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,10 +119,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,10 +130,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
